--- a/data/primary_data/toc.xlsx
+++ b/data/primary_data/toc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\PostGrad\BSc Hons\4ZOL509_Research\primary_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E266786-5FB8-4FCA-B7A5-3E6BFD712FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28D7C00-488E-4793-8711-DC4A4A259DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-5595" windowWidth="25440" windowHeight="15270" xr2:uid="{05975E39-99C1-4D5F-9BE1-3E2B19B17949}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{05975E39-99C1-4D5F-9BE1-3E2B19B17949}"/>
   </bookViews>
   <sheets>
     <sheet name="toc" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="31">
   <si>
     <t>site</t>
   </si>
@@ -61,6 +61,63 @@
   </si>
   <si>
     <t>ash_weight</t>
+  </si>
+  <si>
+    <t>25.42</t>
+  </si>
+  <si>
+    <t>24.45</t>
+  </si>
+  <si>
+    <t>september</t>
+  </si>
+  <si>
+    <t>28.08</t>
+  </si>
+  <si>
+    <t>26.35</t>
+  </si>
+  <si>
+    <t>25.48</t>
+  </si>
+  <si>
+    <t>24.48</t>
+  </si>
+  <si>
+    <t>25.89</t>
+  </si>
+  <si>
+    <t>24.63</t>
+  </si>
+  <si>
+    <t>24.88</t>
+  </si>
+  <si>
+    <t>23.5</t>
+  </si>
+  <si>
+    <t>31.65</t>
+  </si>
+  <si>
+    <t>28.63</t>
+  </si>
+  <si>
+    <t>23.74</t>
+  </si>
+  <si>
+    <t>23.04</t>
+  </si>
+  <si>
+    <t>28.16</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>28.82</t>
+  </si>
+  <si>
+    <t>27.87</t>
   </si>
 </sst>
 </file>
@@ -116,8 +173,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}" name="Table1" displayName="Table1" ref="A1:F26" totalsRowShown="0">
-  <autoFilter ref="A1:F26" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0">
+  <autoFilter ref="A1:F34" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E16">
     <sortCondition ref="E1:E16"/>
   </sortState>
@@ -430,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6FC714-7E85-46D7-BE93-FA19EA717B3F}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -939,6 +996,186 @@
         <v>9</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/primary_data/toc.xlsx
+++ b/data/primary_data/toc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28D7C00-488E-4793-8711-DC4A4A259DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D57506-94BB-4C9D-9B3D-908EE15DCAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{05975E39-99C1-4D5F-9BE1-3E2B19B17949}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
   <si>
     <t>site</t>
   </si>
@@ -118,6 +118,144 @@
   </si>
   <si>
     <t>27.87</t>
+  </si>
+  <si>
+    <t>23.79</t>
+  </si>
+  <si>
+    <t>22.67</t>
+  </si>
+  <si>
+    <t>23.94</t>
+  </si>
+  <si>
+    <t>20.94</t>
+  </si>
+  <si>
+    <t>20.43</t>
+  </si>
+  <si>
+    <t>25.3</t>
+  </si>
+  <si>
+    <t>22.66</t>
+  </si>
+  <si>
+    <t>20.98</t>
+  </si>
+  <si>
+    <t>19.52</t>
+  </si>
+  <si>
+    <t>22.13</t>
+  </si>
+  <si>
+    <t>20.87</t>
+  </si>
+  <si>
+    <t>19.55</t>
+  </si>
+  <si>
+    <t>19.07</t>
+  </si>
+  <si>
+    <t>17.08</t>
+  </si>
+  <si>
+    <t>16.71</t>
+  </si>
+  <si>
+    <t>21.4</t>
+  </si>
+  <si>
+    <t>20.92</t>
+  </si>
+  <si>
+    <t>20.72</t>
+  </si>
+  <si>
+    <t>20.23</t>
+  </si>
+  <si>
+    <t>23.32</t>
+  </si>
+  <si>
+    <t>22.77</t>
+  </si>
+  <si>
+    <t>26.25</t>
+  </si>
+  <si>
+    <t>25.11</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>27.9</t>
+  </si>
+  <si>
+    <t>22.42</t>
+  </si>
+  <si>
+    <t>21.63</t>
+  </si>
+  <si>
+    <t>25.12</t>
+  </si>
+  <si>
+    <t>24.64</t>
+  </si>
+  <si>
+    <t>25.25</t>
+  </si>
+  <si>
+    <t>24.53</t>
+  </si>
+  <si>
+    <t>25.17</t>
+  </si>
+  <si>
+    <t>26.54</t>
+  </si>
+  <si>
+    <t>26.1</t>
+  </si>
+  <si>
+    <t>25.36</t>
+  </si>
+  <si>
+    <t>23.06</t>
+  </si>
+  <si>
+    <t>22.19</t>
+  </si>
+  <si>
+    <t>21.31</t>
+  </si>
+  <si>
+    <t>21.18</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>27.48</t>
+  </si>
+  <si>
+    <t>24.96</t>
+  </si>
+  <si>
+    <t>27.54</t>
+  </si>
+  <si>
+    <t>26.43</t>
+  </si>
+  <si>
+    <t>22.49</t>
+  </si>
+  <si>
+    <t>21.68</t>
   </si>
 </sst>
 </file>
@@ -523,11 +661,11 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>23.79</v>
-      </c>
-      <c r="D2">
-        <v>22.67</v>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -543,11 +681,11 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>24.48</v>
-      </c>
-      <c r="D3">
-        <v>23.94</v>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -563,11 +701,11 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>20.94</v>
-      </c>
-      <c r="D4">
-        <v>20.43</v>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -583,11 +721,11 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>25.3</v>
-      </c>
-      <c r="D5">
-        <v>22.66</v>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -603,11 +741,11 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>20.98</v>
-      </c>
-      <c r="D6">
-        <v>19.52</v>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -623,11 +761,11 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>22.13</v>
-      </c>
-      <c r="D7">
-        <v>20.87</v>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -643,11 +781,11 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>19.55</v>
-      </c>
-      <c r="D8">
-        <v>19.07</v>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -663,11 +801,11 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9">
-        <v>17.079999999999998</v>
-      </c>
-      <c r="D9">
-        <v>16.71</v>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -683,11 +821,11 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10">
-        <v>21.4</v>
-      </c>
-      <c r="D10">
-        <v>20.92</v>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -703,11 +841,11 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>20.72</v>
-      </c>
-      <c r="D11">
-        <v>20.23</v>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -723,11 +861,11 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12">
-        <v>23.32</v>
-      </c>
-      <c r="D12">
-        <v>22.77</v>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -743,11 +881,11 @@
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13">
-        <v>26.25</v>
-      </c>
-      <c r="D13">
-        <v>25.11</v>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -763,11 +901,11 @@
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14">
-        <v>28.9</v>
-      </c>
-      <c r="D14">
-        <v>27.9</v>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -783,11 +921,11 @@
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15">
-        <v>22.42</v>
-      </c>
-      <c r="D15">
-        <v>21.63</v>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -803,11 +941,11 @@
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16">
-        <v>25.12</v>
-      </c>
-      <c r="D16">
-        <v>24.64</v>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -823,11 +961,11 @@
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>25.25</v>
-      </c>
-      <c r="D17">
-        <v>24.53</v>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -843,11 +981,11 @@
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18">
-        <v>25.17</v>
-      </c>
-      <c r="D18">
-        <v>24.64</v>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>59</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -863,11 +1001,11 @@
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19">
-        <v>26.54</v>
-      </c>
-      <c r="D19">
-        <v>26.1</v>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -883,11 +1021,11 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20">
-        <v>25.36</v>
-      </c>
-      <c r="D20">
-        <v>23.06</v>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
+        <v>66</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -903,11 +1041,11 @@
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>22.19</v>
-      </c>
-      <c r="D21">
-        <v>21.31</v>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>68</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -923,11 +1061,11 @@
       <c r="B22">
         <v>3</v>
       </c>
-      <c r="C22">
-        <v>21.18</v>
-      </c>
-      <c r="D22">
-        <v>19.600000000000001</v>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -943,11 +1081,11 @@
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>27.48</v>
-      </c>
-      <c r="D23">
-        <v>24.96</v>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -963,11 +1101,11 @@
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24">
-        <v>27.54</v>
-      </c>
-      <c r="D24">
-        <v>26.43</v>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -983,11 +1121,11 @@
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25">
-        <v>22.49</v>
-      </c>
-      <c r="D25">
-        <v>21.68</v>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>76</v>
       </c>
       <c r="E25">
         <v>3</v>

--- a/data/primary_data/toc.xlsx
+++ b/data/primary_data/toc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D57506-94BB-4C9D-9B3D-908EE15DCAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A76E21B-8D6C-464F-8B1A-30D4C606504F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{05975E39-99C1-4D5F-9BE1-3E2B19B17949}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="147">
   <si>
     <t>site</t>
   </si>
@@ -256,6 +256,216 @@
   </si>
   <si>
     <t>21.68</t>
+  </si>
+  <si>
+    <t>21.07</t>
+  </si>
+  <si>
+    <t>31.64</t>
+  </si>
+  <si>
+    <t>29.83</t>
+  </si>
+  <si>
+    <t>24.35</t>
+  </si>
+  <si>
+    <t>29.45</t>
+  </si>
+  <si>
+    <t>25.15</t>
+  </si>
+  <si>
+    <t>31.31</t>
+  </si>
+  <si>
+    <t>27.22</t>
+  </si>
+  <si>
+    <t>24.28</t>
+  </si>
+  <si>
+    <t>24.03</t>
+  </si>
+  <si>
+    <t>29.96</t>
+  </si>
+  <si>
+    <t>31.02</t>
+  </si>
+  <si>
+    <t>24.82</t>
+  </si>
+  <si>
+    <t>28.90</t>
+  </si>
+  <si>
+    <t>24.11</t>
+  </si>
+  <si>
+    <t>29.25</t>
+  </si>
+  <si>
+    <t>30.71</t>
+  </si>
+  <si>
+    <t>20.90</t>
+  </si>
+  <si>
+    <t>october</t>
+  </si>
+  <si>
+    <t>december</t>
+  </si>
+  <si>
+    <t>24.50</t>
+  </si>
+  <si>
+    <t>20.71</t>
+  </si>
+  <si>
+    <t>27.84</t>
+  </si>
+  <si>
+    <t>21.02</t>
+  </si>
+  <si>
+    <t>22.96</t>
+  </si>
+  <si>
+    <t>20.05</t>
+  </si>
+  <si>
+    <t>22.60</t>
+  </si>
+  <si>
+    <t>19.71</t>
+  </si>
+  <si>
+    <t>20.64</t>
+  </si>
+  <si>
+    <t>27.61</t>
+  </si>
+  <si>
+    <t>20.46</t>
+  </si>
+  <si>
+    <t>24.23</t>
+  </si>
+  <si>
+    <t>20.11</t>
+  </si>
+  <si>
+    <t>22.01</t>
+  </si>
+  <si>
+    <t>20.82</t>
+  </si>
+  <si>
+    <t>27.52</t>
+  </si>
+  <si>
+    <t>26.31</t>
+  </si>
+  <si>
+    <t>23.37</t>
+  </si>
+  <si>
+    <t>23.18</t>
+  </si>
+  <si>
+    <t>27.31</t>
+  </si>
+  <si>
+    <t>20.81</t>
+  </si>
+  <si>
+    <t>20.63</t>
+  </si>
+  <si>
+    <t>27.07</t>
+  </si>
+  <si>
+    <t>23.16</t>
+  </si>
+  <si>
+    <t>25.75</t>
+  </si>
+  <si>
+    <t>27.09</t>
+  </si>
+  <si>
+    <t>20.51</t>
+  </si>
+  <si>
+    <t>21.65</t>
+  </si>
+  <si>
+    <t>19.79</t>
+  </si>
+  <si>
+    <t>january</t>
+  </si>
+  <si>
+    <t>february</t>
+  </si>
+  <si>
+    <t>30.01</t>
+  </si>
+  <si>
+    <t>30.87</t>
+  </si>
+  <si>
+    <t>29.40</t>
+  </si>
+  <si>
+    <t>21.51</t>
+  </si>
+  <si>
+    <t>20.59</t>
+  </si>
+  <si>
+    <t>26.06</t>
+  </si>
+  <si>
+    <t>26.13</t>
+  </si>
+  <si>
+    <t>27.50</t>
+  </si>
+  <si>
+    <t>21.80</t>
+  </si>
+  <si>
+    <t>29.16</t>
+  </si>
+  <si>
+    <t>29.65</t>
+  </si>
+  <si>
+    <t>27.92</t>
+  </si>
+  <si>
+    <t>21.21</t>
+  </si>
+  <si>
+    <t>20.39</t>
+  </si>
+  <si>
+    <t>25.82</t>
+  </si>
+  <si>
+    <t>21.70</t>
+  </si>
+  <si>
+    <t>27.24</t>
+  </si>
+  <si>
+    <t>25.84</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -311,18 +521,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0">
-  <autoFilter ref="A1:F34" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}" name="Table1" displayName="Table1" ref="A1:G67" totalsRowShown="0">
+  <autoFilter ref="A1:G67" xr:uid="{276F16B5-607F-437A-8D86-DD4A65E2B621}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E16">
     <sortCondition ref="E1:E16"/>
   </sortState>
-  <tableColumns count="6">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1C037EE9-84AC-420E-91AB-9C774C7B30DB}" name="site"/>
     <tableColumn id="2" xr3:uid="{E05CEB40-421B-4131-B707-A5EFDF97F38B}" name="replicate"/>
     <tableColumn id="3" xr3:uid="{DC2B6A03-3874-4A41-87A5-6FCEB2C803F1}" name="dry_weight"/>
     <tableColumn id="4" xr3:uid="{DC28E870-5123-478B-92EA-796E593812A0}" name="ash_weight"/>
     <tableColumn id="5" xr3:uid="{ABE18BBF-6C35-4F71-B1F9-76B1350C0B5A}" name="sample"/>
     <tableColumn id="6" xr3:uid="{779B9AAD-7C94-498D-9004-484C566D0AB8}" name="month"/>
+    <tableColumn id="7" xr3:uid="{555D3E39-DD20-438B-962B-70564C7E175D}" name="year"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -625,16 +836,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6FC714-7E85-46D7-BE93-FA19EA717B3F}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,8 +865,11 @@
       <c r="F1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -673,8 +888,11 @@
       <c r="F2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -693,8 +911,11 @@
       <c r="F3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -713,8 +934,11 @@
       <c r="F4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -733,8 +957,11 @@
       <c r="F5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -753,8 +980,11 @@
       <c r="F6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -773,8 +1003,11 @@
       <c r="F7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -793,8 +1026,11 @@
       <c r="F8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -813,8 +1049,11 @@
       <c r="F9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -833,8 +1072,11 @@
       <c r="F10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -853,8 +1095,11 @@
       <c r="F11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -873,8 +1118,11 @@
       <c r="F12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -893,8 +1141,11 @@
       <c r="F13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -913,8 +1164,11 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -933,8 +1187,11 @@
       <c r="F15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -953,8 +1210,11 @@
       <c r="F16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -973,8 +1233,11 @@
       <c r="F17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -993,8 +1256,11 @@
       <c r="F18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -1013,8 +1279,11 @@
       <c r="F19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1033,8 +1302,11 @@
       <c r="F20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1325,11 @@
       <c r="F21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1073,8 +1348,11 @@
       <c r="F22" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1093,8 +1371,11 @@
       <c r="F23" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1113,8 +1394,11 @@
       <c r="F24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1133,8 +1417,11 @@
       <c r="F25" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -1153,8 +1440,11 @@
       <c r="F26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -1173,8 +1463,11 @@
       <c r="F27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1193,8 +1486,11 @@
       <c r="F28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1213,8 +1509,11 @@
       <c r="F29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1233,8 +1532,11 @@
       <c r="F30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1555,11 @@
       <c r="F31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1273,8 +1578,11 @@
       <c r="F32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1293,8 +1601,11 @@
       <c r="F33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1312,6 +1623,768 @@
       </c>
       <c r="F34" t="s">
         <v>14</v>
+      </c>
+      <c r="G34">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>95</v>
+      </c>
+      <c r="G36">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+      <c r="F45" t="s">
+        <v>96</v>
+      </c>
+      <c r="G45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47">
+        <v>6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>96</v>
+      </c>
+      <c r="G48">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G52">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>126</v>
+      </c>
+      <c r="G53">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G55">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" t="s">
+        <v>101</v>
+      </c>
+      <c r="E56">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>126</v>
+      </c>
+      <c r="G56">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>119</v>
+      </c>
+      <c r="E57">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>127</v>
+      </c>
+      <c r="G60">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+      <c r="F61" t="s">
+        <v>127</v>
+      </c>
+      <c r="G61">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>127</v>
+      </c>
+      <c r="G62">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>127</v>
+      </c>
+      <c r="G63">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>127</v>
+      </c>
+      <c r="G64">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>127</v>
+      </c>
+      <c r="G65">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+      <c r="F66" t="s">
+        <v>127</v>
+      </c>
+      <c r="G66">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>127</v>
+      </c>
+      <c r="G67">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
